--- a/import-template.xlsx
+++ b/import-template.xlsx
@@ -39,7 +39,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="008A8D93"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6A23C"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,12 +88,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,7 +212,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>2021</t>
+        <t>ОБЯЗАТЕЛЬНО. 2021 — год выпуска</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -219,17 +227,17 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>1500 — обязателен для ДВС</t>
+        <t>ОБЯЗАТЕЛЬНО ПО УСЛОВИЮ. 1500. Обязателен для бензина и дизеля. Для электрокара оставьте пустым</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>150</t>
+        <t>ОБЯЗАТЕЛЬНО ПО УСЛОВИЮ. 150. Обязательна мощность — в л.с. ИЛИ в кВт</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>для электрокаров</t>
+        <t>ОБЯЗАТЕЛЬНО ПО УСЛОВИЮ. 160. Для электрокаров вместо л.с.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
@@ -675,7 +683,7 @@
           <t>комплектация</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>год</t>
         </is>
@@ -690,17 +698,17 @@
           <t>пробег_км</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>объём_см3</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>мощность_лс</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>мощность_квт</t>
         </is>
@@ -802,327 +810,327 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>jp</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Toyota</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Corolla Fielder</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Hybrid G</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>48000</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>бензин</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>вариатор</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>передний</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>универсал</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>белый</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>30215</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>JU MIE</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="U2" s="4" t="n">
         <v>1200000</v>
       </c>
-      <c r="V2" s="3" t="n"/>
-      <c r="W2" s="3" t="n"/>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="V2" s="4" t="n"/>
+      <c r="W2" s="4" t="n"/>
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Z2" s="3" t="n"/>
-      <c r="AA2" s="3" t="inlineStr">
+      <c r="Z2" s="4" t="n"/>
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>Новосибирск</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="n"/>
-      <c r="AC2" s="3" t="inlineStr">
+      <c r="AB2" s="4" t="n"/>
+      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>A2 — вмятина на правой двери</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>jp</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Toyota</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Harrier</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>2020</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>62000</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>бензин</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>автомат</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>полный</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>внедорожник</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>чёрный</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>44120</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>USS Tokyo</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="4" t="n">
         <v>2600000</v>
       </c>
-      <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="V3" s="4" t="n"/>
+      <c r="W3" s="4" t="n"/>
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="Z3" s="4" t="n"/>
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>Москва</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="n"/>
-      <c r="AC3" s="3" t="n"/>
+      <c r="AB3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>kr</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Hyundai</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Ioniq 5</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Long Range</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>2023</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>21000</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="n">
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>электро</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>автомат</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>полный</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>внедорожник</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>серый</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="Q4" s="4" t="n"/>
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>KR-9981</t>
         </is>
       </c>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n">
+      <c r="T4" s="4" t="n"/>
+      <c r="U4" s="4" t="n">
         <v>38000000</v>
       </c>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="V4" s="4" t="n"/>
+      <c r="W4" s="4" t="n"/>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n"/>
-      <c r="AA4" s="3" t="inlineStr">
+      <c r="Z4" s="4" t="n"/>
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>Владивосток</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="n"/>
-      <c r="AC4" s="3" t="n"/>
+      <c r="AB4" s="4" t="n"/>
+      <c r="AC4" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="9">
@@ -1165,171 +1173,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Как заполнять шаблон</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
+      <c r="A2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1. Строка 1 — названия колонок. Не удаляйте и не переименовывайте её:</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   импорт находит колонки именно по этим названиям. Порядок колонок можно менять.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Наведите курсор на заголовок — во всплывающей подсказке написано, что вписывать.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2. Данные вносите со второй строки. Три примера уже заполнены —</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   правьте их или удалите и впишите своё.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>3. Обязательны только четыре колонки (выделены синим): страна, марка, модель, цена.</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3. Синие колонки обязательны всегда:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Остальное можно оставить пустым.</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   страна, марка, модель, цена, год, и мощность — в л.с. или в кВт.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>4. Цена — в валюте страны: Япония в иенах, Корея в вонах, Китай в юанях.</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4. Янтарная колонка «объём_см3» обязательна для бензина и дизеля.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Для электрокара оставьте её пустой, но заполните «мощность_квт»</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>5. Доставку обычно указывать не нужно:</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   и поставьте «да» в колонке «электрокар».</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Серые колонки можно не заполнять.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Минимальная строка для ДВС: jp / Toyota / Prius / 1000000 / 2021 / 100 / 1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>5. Цена — в валюте страны: Япония в иенах, Корея в вонах, Китай в юанях.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>6. Доставку обычно указывать не нужно:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Япония — подтянется по названию аукциона из справочника;</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Корея — считается по цене авто;</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   • Китай — фиксированная.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Колонка «доставка» нужна, только если аукцион не из списка.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>6. Возраст обычно оставляйте пустым — он считается по году и месяцу выпуска.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>7. Объём двигателя обязателен для бензина и дизеля. Для электрокара оставьте пустым,</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   но заполните «мощность_квт» и поставьте «да» в колонке «электрокар».</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>7. Возраст обычно оставляйте пустым — он считается по году и месяцу выпуска.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Загрузка: откройте калькулятор → режим «База» → кнопка «Таблица» → выберите этот файл.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Перед загрузкой приложение покажет предпросмотр: сколько строк готово,</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>где ошибки и какая цена «под ключ» получилась по каждой машине.</t>
         </is>

--- a/import-template.xlsx
+++ b/import-template.xlsx
@@ -262,7 +262,7 @@
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>седан / внедорожник / универсал / хэтчбек / купе / минивэн / пикап</t>
+        <t>ОБЯЗАТЕЛЬНО. седан / внедорожник / универсал / хэтчбек / купе / минивэн / пикап / фургон / кабриолет</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -733,7 +733,7 @@
           <t>привод</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>кузов</t>
         </is>
@@ -1173,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1240,131 +1240,138 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   страна, марка, модель, цена, год, и мощность — в л.с. или в кВт.</t>
+          <t xml:space="preserve">   страна, марка, модель, цена, год, кузов, и мощность — в л.с. или в кВт.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Кузов нужен, чтобы авто попадало в подборки по типу («кроссоверы до 3 млн»).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>4. Янтарная колонка «объём_см3» обязательна для бензина и дизеля.</t>
-        </is>
-      </c>
+      <c r="A13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Для электрокара оставьте её пустой, но заполните «мощность_квт»</t>
+          <t>4. Янтарная колонка «объём_см3» обязательна для бензина и дизеля.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Для электрокара оставьте её пустой, но заполните «мощность_квт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">   и поставьте «да» в колонке «электрокар».</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Серые колонки можно не заполнять.</t>
-        </is>
-      </c>
+      <c r="A17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Серые колонки можно не заполнять.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Минимальная строка для ДВС: jp / Toyota / Prius / 1000000 / 2021 / 100 / 1800</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>5. Цена — в валюте страны: Япония в иенах, Корея в вонах, Китай в юанях.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>6. Доставку обычно указывать не нужно:</t>
-        </is>
-      </c>
+      <c r="A22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Япония — подтянется по названию аукциона из справочника;</t>
+          <t>6. Доставку обычно указывать не нужно:</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Корея — считается по цене авто;</t>
+          <t xml:space="preserve">   • Япония — подтянется по названию аукциона из справочника;</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Китай — фиксированная.</t>
+          <t xml:space="preserve">   • Корея — считается по цене авто;</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">   • Китай — фиксированная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Колонка «доставка» нужна, только если аукцион не из списка.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>7. Возраст обычно оставляйте пустым — он считается по году и месяцу выпуска.</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Загрузка: откройте калькулятор → режим «База» → кнопка «Таблица» → выберите этот файл.</t>
-        </is>
-      </c>
+      <c r="A31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Перед загрузкой приложение покажет предпросмотр: сколько строк готово,</t>
+          <t>Загрузка: откройте калькулятор → режим «База» → кнопка «Таблица» → выберите этот файл.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Перед загрузкой приложение покажет предпросмотр: сколько строк готово,</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>где ошибки и какая цена «под ключ» получилась по каждой машине.</t>
         </is>
